--- a/duoki_editor/resources/data/blank/海洋-一般疑问句_肯定答句认读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/海洋-一般疑问句_肯定答句认读-1-blank.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>stage_id</t>
   </si>
@@ -61,10 +61,10 @@
     <t>一般疑问句_认读_1_问_2</t>
   </si>
   <si>
-    <t>一般疑问句_认读_1_问_3</t>
-  </si>
-  <si>
-    <t>一般疑问句_认读_1_答</t>
+    <t>(一般疑问句_认读_1_问_答案)</t>
+  </si>
+  <si>
+    <t>一般疑问句_认读_1_帮助</t>
   </si>
   <si>
     <t>结束语_1</t>
@@ -82,37 +82,34 @@
     <t>npc2</t>
   </si>
   <si>
-    <t>哇！宝石精灵坐着彩虹飞来了！{npc2_name}，快来接受魔法挑战，赢取魔法宝石吧！第一个魔法问题来咯，{sentence_question_en}?</t>
+    <t>哇！宝石精灵坐着彩虹飞来了！{npc2_name}，快来接受魔法挑战，赢取魔法宝石吧！第一个魔法问题来咯，{sentence_question_en}</t>
   </si>
   <si>
     <t>叮咚！答对啦！宝石精灵在为你欢呼哟！再来一个更有趣的魔法问题，它是飞鱼吗？Is it a flying fish？</t>
   </si>
   <si>
-    <t>{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>{sentence_answer_en_2}。</t>
-  </si>
-  <si>
-    <t>这一题也答对啦！{user_name}，现在轮到你了！注意看屏幕，要根据屏幕上的提示来回答哦！{sentence_question_en}?</t>
-  </si>
-  <si>
-    <t>哎呀，是调皮的风精灵偷走了你的声音吗？没关系，再大声说一遍吧！{sentence_question_en}?</t>
-  </si>
-  <si>
     <t>{sentence_answer_en_1}</t>
   </si>
   <si>
+    <t>{sentence_answer_en_2}</t>
+  </si>
+  <si>
+    <t>这一题也答对啦！{user_name}，现在轮到你了！注意看屏幕，要根据屏幕上的提示来回答哦！{sentence_question_en}</t>
+  </si>
+  <si>
+    <t>哎呀，是调皮的风精灵偷走了你的声音吗？没关系，再大声说一遍吧！{sentence_question_en}</t>
+  </si>
+  <si>
     <t>我来帮你吧！ {sentence_answer_en_1}</t>
   </si>
   <si>
-    <t>恭喜挑战成功！你们赢得了20颗宝石！</t>
-  </si>
-  <si>
-    <t>这次{npc2_name}帮了你，只能得到10颗宝石哦！下次要继续加油！</t>
-  </si>
-  <si>
-    <t>20|10</t>
+    <t>恭喜挑战成功！你们赢得了10颗宝石！</t>
+  </si>
+  <si>
+    <t>这次{npc2_name}帮了你，只能得到5颗宝石哦！下次要继续加油！</t>
+  </si>
+  <si>
+    <t>10|5</t>
   </si>
 </sst>
 </file>
@@ -606,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -623,7 +620,7 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -640,7 +637,7 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -657,7 +654,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -674,7 +671,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
